--- a/tables/hyperparameters.xlsx
+++ b/tables/hyperparameters.xlsx
@@ -458,10 +458,10 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.0005987474910461401</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.0002334586407601625</v>
       </c>
     </row>
     <row r="3">
@@ -479,10 +479,10 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.009699181949451583</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.0001948171764312826</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>6.487185401050272e-05</v>
+        <v>0.001392816601899443</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005383737865838912</v>
+        <v>0.001248739640549139</v>
       </c>
     </row>
     <row r="5">
@@ -521,10 +521,10 @@
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.001792701950273333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.00172065947304378</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.001392816601899443</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.001248739640549139</v>
       </c>
     </row>
     <row r="7">
@@ -563,10 +563,10 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>1.074472913597675e-06</v>
+        <v>0.002546123223585131</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001506563811197928</v>
+        <v>0.001289486564472573</v>
       </c>
     </row>
     <row r="8">
@@ -584,10 +584,10 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>6.487185401050272e-05</v>
+        <v>0.0002701266375241966</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0005383737865838912</v>
+        <v>0.0001987526507177876</v>
       </c>
     </row>
     <row r="9">
@@ -605,10 +605,10 @@
         <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.001011519849458446</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.001316859408363818</v>
       </c>
     </row>
     <row r="10">
@@ -619,17 +619,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tanh</t>
+          <t>relu</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.002019418623462585</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.001285569636097186</v>
       </c>
     </row>
     <row r="11">
@@ -647,10 +647,10 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0002781857010763975</v>
+        <v>0.0002446614120759791</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004050104259141605</v>
+        <v>0.00196406863921533</v>
       </c>
     </row>
     <row r="12">
@@ -668,10 +668,10 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.0003263226265768902</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.002243307784788722</v>
       </c>
     </row>
     <row r="13">
@@ -689,10 +689,10 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.0002189391590001696</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.001220908709473445</v>
       </c>
     </row>
     <row r="14">
@@ -710,10 +710,10 @@
         <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.0001801331454488317</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.001800294869410611</v>
       </c>
     </row>
     <row r="15">
@@ -724,17 +724,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tanh</t>
+          <t>relu</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.0009216691917477486</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.001790215422109308</v>
       </c>
     </row>
     <row r="16">
@@ -752,10 +752,10 @@
         <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002342384984711291</v>
+        <v>0.0004383323192443003</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0006672367170464204</v>
+        <v>0.005385990345812957</v>
       </c>
     </row>
   </sheetData>

--- a/tables/hyperparameters.xlsx
+++ b/tables/hyperparameters.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>Ressource</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
